--- a/exposures_meta_analysis_ovarian_combined.xlsx
+++ b/exposures_meta_analysis_ovarian_combined.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>Exposure</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>caffeine</t>
+  </si>
+  <si>
+    <t>red_meat</t>
   </si>
   <si>
     <t>potassium</t>
@@ -500,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1423,25 +1426,25 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31">
-        <v>2.4</v>
+        <v>1.24</v>
       </c>
       <c r="D31">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="E31">
-        <v>4.71</v>
+        <v>1.35</v>
       </c>
       <c r="H31">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>269315</v>
+        <v>24201</v>
       </c>
       <c r="K31">
-        <v>7180</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1449,25 +1452,25 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32">
-        <v>2.79</v>
+        <v>2.4</v>
       </c>
       <c r="D32">
         <v>1.22</v>
       </c>
       <c r="E32">
-        <v>4.88</v>
+        <v>4.71</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J32">
-        <v>200</v>
+        <v>269315</v>
       </c>
       <c r="K32">
-        <v>100</v>
+        <v>7180</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1478,21 +1481,47 @@
         <v>1</v>
       </c>
       <c r="C33">
+        <v>2.79</v>
+      </c>
+      <c r="D33">
+        <v>1.22</v>
+      </c>
+      <c r="E33">
+        <v>4.88</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>200</v>
+      </c>
+      <c r="K33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
         <v>3.24</v>
       </c>
-      <c r="D33">
+      <c r="D34">
         <v>1.13</v>
       </c>
-      <c r="E33">
+      <c r="E34">
         <v>5.81</v>
       </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
-      <c r="J33">
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="J34">
         <v>176</v>
       </c>
-      <c r="K33">
+      <c r="K34">
         <v>96</v>
       </c>
     </row>

--- a/exposures_meta_analysis_ovarian_combined.xlsx
+++ b/exposures_meta_analysis_ovarian_combined.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Exposure</t>
   </si>
@@ -49,33 +49,72 @@
     <t>total Cases</t>
   </si>
   <si>
+    <t>magnesium</t>
+  </si>
+  <si>
+    <t>selenium</t>
+  </si>
+  <si>
+    <t>potassium</t>
+  </si>
+  <si>
+    <t>lactobacillus</t>
+  </si>
+  <si>
+    <t>soy</t>
+  </si>
+  <si>
+    <t>vitamin_b6</t>
+  </si>
+  <si>
     <t>legumes</t>
   </si>
   <si>
     <t>antioxidants</t>
   </si>
   <si>
+    <t>vitamin_e</t>
+  </si>
+  <si>
+    <t>lutein</t>
+  </si>
+  <si>
     <t>calcium</t>
   </si>
   <si>
-    <t>lutein</t>
-  </si>
-  <si>
     <t>mushrooms</t>
   </si>
   <si>
     <t>olive</t>
   </si>
   <si>
+    <t>vitamin_c</t>
+  </si>
+  <si>
+    <t>tea</t>
+  </si>
+  <si>
+    <t>vitamin_d</t>
+  </si>
+  <si>
+    <t>melatonin</t>
+  </si>
+  <si>
     <t>beta-carotene</t>
   </si>
   <si>
+    <t>fish_oil</t>
+  </si>
+  <si>
     <t>folic_acid</t>
   </si>
   <si>
     <t>mediterranean_diet</t>
   </si>
   <si>
+    <t>vitamin_a</t>
+  </si>
+  <si>
     <t>caffeine</t>
   </si>
   <si>
@@ -88,10 +127,19 @@
     <t>dairy</t>
   </si>
   <si>
+    <t>red_meat</t>
+  </si>
+  <si>
     <t>eggs</t>
   </si>
   <si>
     <t>non-alcoholic_fermented_foods</t>
+  </si>
+  <si>
+    <t>iron</t>
+  </si>
+  <si>
+    <t>dehydroepiandrosterone</t>
   </si>
 </sst>
 </file>
@@ -449,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -492,25 +540,25 @@
         <v>11</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>0.6</v>
+        <v>0.16</v>
       </c>
       <c r="D2">
-        <v>0.25</v>
+        <v>0.03</v>
       </c>
       <c r="E2">
-        <v>1.43</v>
+        <v>0.73</v>
       </c>
       <c r="H2">
-        <v>86.7</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>63479</v>
+        <v>66450</v>
       </c>
       <c r="K2">
-        <v>506</v>
+        <v>25509</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -518,34 +566,34 @@
         <v>12</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>0.62</v>
+        <v>0.23</v>
       </c>
       <c r="D3">
-        <v>0.39</v>
+        <v>0.06</v>
       </c>
       <c r="E3">
-        <v>0.99</v>
+        <v>0.93</v>
       </c>
       <c r="F3">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>4.94</v>
+        <v>7452916.73</v>
       </c>
       <c r="H3">
-        <v>85.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="I3">
-        <v>0.02324713824841669</v>
+        <v>0.2282188608675652</v>
       </c>
       <c r="J3">
-        <v>523871</v>
+        <v>1947</v>
       </c>
       <c r="K3">
-        <v>2791</v>
+        <v>768</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -553,34 +601,25 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>0.66</v>
+        <v>0.35</v>
       </c>
       <c r="D4">
-        <v>0.57</v>
+        <v>0.12</v>
       </c>
       <c r="E4">
-        <v>0.75</v>
-      </c>
-      <c r="F4">
-        <v>0.53</v>
-      </c>
-      <c r="G4">
-        <v>0.82</v>
+        <v>0.98</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4">
-        <v>0.1549127808728178</v>
-      </c>
       <c r="J4">
-        <v>41576</v>
+        <v>232908</v>
       </c>
       <c r="K4">
-        <v>4134</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -588,34 +627,25 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="D5">
-        <v>0.48</v>
+        <v>0.16</v>
       </c>
       <c r="E5">
-        <v>0.98</v>
-      </c>
-      <c r="F5">
-        <v>0.14</v>
-      </c>
-      <c r="G5">
-        <v>3.33</v>
+        <v>0.87</v>
       </c>
       <c r="H5">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="I5">
-        <v>0.06371753035051776</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>529715</v>
+        <v>360</v>
       </c>
       <c r="K5">
-        <v>3624</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -623,25 +653,25 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>0.71</v>
+        <v>0.41</v>
       </c>
       <c r="D6">
-        <v>0.55</v>
+        <v>0.25</v>
       </c>
       <c r="E6">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J6">
-        <v>1000</v>
+        <v>1906</v>
       </c>
       <c r="K6">
-        <v>500</v>
+        <v>754</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -652,22 +682,22 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <v>0.71</v>
+        <v>0.51</v>
       </c>
       <c r="D7">
-        <v>0.53</v>
+        <v>0.25</v>
       </c>
       <c r="E7">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>3442</v>
+        <v>73909</v>
       </c>
       <c r="K7">
-        <v>1031</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -675,34 +705,25 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>0.74</v>
+        <v>0.6</v>
       </c>
       <c r="D8">
-        <v>0.6</v>
+        <v>0.25</v>
       </c>
       <c r="E8">
-        <v>0.92</v>
-      </c>
-      <c r="F8">
-        <v>0.41</v>
-      </c>
-      <c r="G8">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="H8">
-        <v>69.3</v>
-      </c>
-      <c r="I8">
-        <v>0.007405482745728637</v>
+        <v>86.7</v>
       </c>
       <c r="J8">
-        <v>611872</v>
+        <v>63479</v>
       </c>
       <c r="K8">
-        <v>4692</v>
+        <v>506</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -710,34 +731,34 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>0.91</v>
+        <v>0.62</v>
       </c>
       <c r="D9">
-        <v>0.72</v>
+        <v>0.39</v>
       </c>
       <c r="E9">
-        <v>1.14</v>
+        <v>0.99</v>
       </c>
       <c r="F9">
-        <v>0.45</v>
+        <v>0.08</v>
       </c>
       <c r="G9">
-        <v>1.85</v>
+        <v>4.94</v>
       </c>
       <c r="H9">
-        <v>77.7</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I9">
-        <v>0.4473296420997003</v>
+        <v>0.02324713824841669</v>
       </c>
       <c r="J9">
-        <v>739242</v>
+        <v>523871</v>
       </c>
       <c r="K9">
-        <v>10599</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -745,25 +766,34 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>0.92</v>
+        <v>0.65</v>
       </c>
       <c r="D10">
-        <v>0.72</v>
+        <v>0.48</v>
       </c>
       <c r="E10">
-        <v>1.17</v>
+        <v>0.88</v>
+      </c>
+      <c r="F10">
+        <v>0.25</v>
+      </c>
+      <c r="G10">
+        <v>1.73</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>86.5</v>
+      </c>
+      <c r="I10">
+        <v>0.004299285744058734</v>
       </c>
       <c r="J10">
-        <v>82948</v>
+        <v>657479</v>
       </c>
       <c r="K10">
-        <v>696</v>
+        <v>30006</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -771,34 +801,34 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>0.96</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D11">
-        <v>0.8</v>
+        <v>0.48</v>
       </c>
       <c r="E11">
-        <v>1.14</v>
+        <v>0.98</v>
       </c>
       <c r="F11">
-        <v>0.5600000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="G11">
-        <v>1.64</v>
+        <v>3.33</v>
       </c>
       <c r="H11">
-        <v>71.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I11">
-        <v>0.854887127293174</v>
+        <v>0.06371753035051776</v>
       </c>
       <c r="J11">
-        <v>336054</v>
+        <v>529715</v>
       </c>
       <c r="K11">
-        <v>38479</v>
+        <v>3624</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -806,25 +836,34 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>0.98</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D12">
-        <v>0.73</v>
+        <v>0.53</v>
       </c>
       <c r="E12">
-        <v>1.31</v>
+        <v>0.9</v>
+      </c>
+      <c r="F12">
+        <v>0.31</v>
+      </c>
+      <c r="G12">
+        <v>1.53</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>68.40000000000001</v>
+      </c>
+      <c r="I12">
+        <v>0.9211493833547117</v>
       </c>
       <c r="J12">
-        <v>159957</v>
+        <v>42324</v>
       </c>
       <c r="K12">
-        <v>526</v>
+        <v>4508</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -835,22 +874,22 @@
         <v>1</v>
       </c>
       <c r="C13">
-        <v>1.01</v>
+        <v>0.71</v>
       </c>
       <c r="D13">
-        <v>0.97</v>
+        <v>0.55</v>
       </c>
       <c r="E13">
-        <v>1.05</v>
+        <v>0.9</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>521911</v>
+        <v>1000</v>
       </c>
       <c r="K13">
-        <v>2012</v>
+        <v>500</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -858,34 +897,25 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>1.1</v>
+        <v>0.71</v>
       </c>
       <c r="D14">
-        <v>1.01</v>
+        <v>0.53</v>
       </c>
       <c r="E14">
-        <v>1.21</v>
-      </c>
-      <c r="F14">
-        <v>0.87</v>
-      </c>
-      <c r="G14">
-        <v>1.4</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H14">
-        <v>86.2</v>
-      </c>
-      <c r="I14">
-        <v>0.520477629217017</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>737543</v>
+        <v>3442</v>
       </c>
       <c r="K14">
-        <v>6692</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -893,25 +923,34 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15">
-        <v>1.35</v>
+        <v>0.72</v>
       </c>
       <c r="D15">
-        <v>1.15</v>
+        <v>0.41</v>
       </c>
       <c r="E15">
-        <v>1.57</v>
+        <v>1.29</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>945.6900000000001</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>91.59999999999999</v>
+      </c>
+      <c r="I15">
+        <v>0.4980193314692444</v>
       </c>
       <c r="J15">
-        <v>1014</v>
+        <v>583089</v>
       </c>
       <c r="K15">
-        <v>450</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -919,25 +958,504 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C16">
+        <v>0.79</v>
+      </c>
+      <c r="D16">
+        <v>0.58</v>
+      </c>
+      <c r="E16">
+        <v>1.07</v>
+      </c>
+      <c r="F16">
+        <v>0.26</v>
+      </c>
+      <c r="G16">
+        <v>2.37</v>
+      </c>
+      <c r="H16">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="I16">
+        <v>0.9601614254203764</v>
+      </c>
+      <c r="J16">
+        <v>307213</v>
+      </c>
+      <c r="K16">
+        <v>4002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17">
+        <v>13</v>
+      </c>
+      <c r="C17">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D17">
+        <v>0.73</v>
+      </c>
+      <c r="E17">
+        <v>0.91</v>
+      </c>
+      <c r="F17">
+        <v>0.6</v>
+      </c>
+      <c r="G17">
+        <v>1.09</v>
+      </c>
+      <c r="H17">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="I17">
+        <v>0.00148760463559832</v>
+      </c>
+      <c r="J17">
+        <v>426489</v>
+      </c>
+      <c r="K17">
+        <v>19570</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D18">
+        <v>0.43</v>
+      </c>
+      <c r="E18">
+        <v>1.45</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>456</v>
+      </c>
+      <c r="K18">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19">
+        <v>9</v>
+      </c>
+      <c r="C19">
+        <v>0.87</v>
+      </c>
+      <c r="D19">
+        <v>0.78</v>
+      </c>
+      <c r="E19">
+        <v>0.98</v>
+      </c>
+      <c r="F19">
+        <v>0.65</v>
+      </c>
+      <c r="G19">
+        <v>1.17</v>
+      </c>
+      <c r="H19">
+        <v>76</v>
+      </c>
+      <c r="I19">
+        <v>0.004106812827796204</v>
+      </c>
+      <c r="J19">
+        <v>678322</v>
+      </c>
+      <c r="K19">
+        <v>30201</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>0.9</v>
+      </c>
+      <c r="D20">
+        <v>0.85</v>
+      </c>
+      <c r="E20">
+        <v>0.97</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>66450</v>
+      </c>
+      <c r="K20">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21">
+        <v>10</v>
+      </c>
+      <c r="C21">
+        <v>0.91</v>
+      </c>
+      <c r="D21">
+        <v>0.72</v>
+      </c>
+      <c r="E21">
+        <v>1.14</v>
+      </c>
+      <c r="F21">
+        <v>0.45</v>
+      </c>
+      <c r="G21">
+        <v>1.85</v>
+      </c>
+      <c r="H21">
+        <v>77.7</v>
+      </c>
+      <c r="I21">
+        <v>0.4473296420997003</v>
+      </c>
+      <c r="J21">
+        <v>739242</v>
+      </c>
+      <c r="K21">
+        <v>10599</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>0.92</v>
+      </c>
+      <c r="D22">
+        <v>0.72</v>
+      </c>
+      <c r="E22">
+        <v>1.17</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>82948</v>
+      </c>
+      <c r="K22">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>0.97</v>
+      </c>
+      <c r="D23">
+        <v>0.86</v>
+      </c>
+      <c r="E23">
+        <v>1.09</v>
+      </c>
+      <c r="F23">
+        <v>0.72</v>
+      </c>
+      <c r="G23">
+        <v>1.31</v>
+      </c>
+      <c r="H23">
+        <v>57.3</v>
+      </c>
+      <c r="I23">
+        <v>0.4784202102804355</v>
+      </c>
+      <c r="J23">
+        <v>1588466</v>
+      </c>
+      <c r="K23">
+        <v>9351</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24">
+        <v>12</v>
+      </c>
+      <c r="C24">
+        <v>0.97</v>
+      </c>
+      <c r="D24">
+        <v>0.86</v>
+      </c>
+      <c r="E24">
+        <v>1.09</v>
+      </c>
+      <c r="F24">
+        <v>0.68</v>
+      </c>
+      <c r="G24">
+        <v>1.37</v>
+      </c>
+      <c r="H24">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="I24">
+        <v>0.8701326593934136</v>
+      </c>
+      <c r="J24">
+        <v>380116</v>
+      </c>
+      <c r="K24">
+        <v>39052</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>0.98</v>
+      </c>
+      <c r="D25">
+        <v>0.73</v>
+      </c>
+      <c r="E25">
+        <v>1.31</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>159957</v>
+      </c>
+      <c r="K25">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1.01</v>
+      </c>
+      <c r="D26">
+        <v>0.97</v>
+      </c>
+      <c r="E26">
+        <v>1.05</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>521911</v>
+      </c>
+      <c r="K26">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27">
+        <v>12</v>
+      </c>
+      <c r="C27">
+        <v>1.1</v>
+      </c>
+      <c r="D27">
+        <v>1.01</v>
+      </c>
+      <c r="E27">
+        <v>1.21</v>
+      </c>
+      <c r="F27">
+        <v>0.87</v>
+      </c>
+      <c r="G27">
+        <v>1.4</v>
+      </c>
+      <c r="H27">
+        <v>86.2</v>
+      </c>
+      <c r="I27">
+        <v>0.520477629217017</v>
+      </c>
+      <c r="J27">
+        <v>737543</v>
+      </c>
+      <c r="K27">
+        <v>6692</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>1.24</v>
+      </c>
+      <c r="D28">
+        <v>1.14</v>
+      </c>
+      <c r="E28">
+        <v>1.35</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>1.35</v>
+      </c>
+      <c r="D29">
+        <v>1.15</v>
+      </c>
+      <c r="E29">
+        <v>1.57</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1014</v>
+      </c>
+      <c r="K29">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
         <v>1.52</v>
       </c>
-      <c r="D16">
+      <c r="D30">
         <v>1.19</v>
       </c>
-      <c r="E16">
+      <c r="E30">
         <v>1.92</v>
       </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="J16">
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="J30">
         <v>2108</v>
       </c>
-      <c r="K16">
+      <c r="K30">
         <v>554</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>1.92</v>
+      </c>
+      <c r="D31">
+        <v>1.45</v>
+      </c>
+      <c r="E31">
+        <v>2.47</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>7887</v>
+      </c>
+      <c r="K31">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>2.79</v>
+      </c>
+      <c r="D32">
+        <v>1.22</v>
+      </c>
+      <c r="E32">
+        <v>4.88</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>200</v>
+      </c>
+      <c r="K32">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/exposures_meta_analysis_ovarian_combined.xlsx
+++ b/exposures_meta_analysis_ovarian_combined.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,57 +429,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>number studies</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -724,7 +736,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02324713824841671</v>
+        <v>0.02324713824841669</v>
       </c>
       <c r="J9" t="n">
         <v>523871</v>
@@ -761,7 +773,7 @@
         <v>86.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0.004299285744058736</v>
+        <v>0.004299285744058734</v>
       </c>
       <c r="J10" t="n">
         <v>657479</v>
@@ -773,81 +785,81 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>lutein</t>
+          <t>calcium</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.48</v>
+        <v>0.53</v>
       </c>
       <c r="E11" t="n">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="F11" t="n">
-        <v>0.14</v>
+        <v>0.31</v>
       </c>
       <c r="G11" t="n">
-        <v>3.33</v>
+        <v>1.53</v>
       </c>
       <c r="H11" t="n">
-        <v>88.40000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06371753035051776</v>
+        <v>0.9211493833547117</v>
       </c>
       <c r="J11" t="n">
-        <v>529715</v>
+        <v>42324</v>
       </c>
       <c r="K11" t="n">
-        <v>3624</v>
+        <v>4508</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>calcium</t>
+          <t>lutein</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.53</v>
+        <v>0.48</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9</v>
+        <v>0.98</v>
       </c>
       <c r="F12" t="n">
-        <v>0.31</v>
+        <v>0.14</v>
       </c>
       <c r="G12" t="n">
-        <v>1.53</v>
+        <v>3.33</v>
       </c>
       <c r="H12" t="n">
-        <v>68.40000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9211493833547117</v>
+        <v>0.06371753035051776</v>
       </c>
       <c r="J12" t="n">
-        <v>42324</v>
+        <v>529715</v>
       </c>
       <c r="K12" t="n">
-        <v>4508</v>
+        <v>3624</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mushrooms</t>
+          <t>olive</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -857,10 +869,10 @@
         <v>0.71</v>
       </c>
       <c r="D13" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -869,16 +881,16 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>1000</v>
+        <v>3442</v>
       </c>
       <c r="K13" t="n">
-        <v>500</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>olive</t>
+          <t>mushrooms</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -888,10 +900,10 @@
         <v>0.71</v>
       </c>
       <c r="D14" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
@@ -900,10 +912,10 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>3442</v>
+        <v>1000</v>
       </c>
       <c r="K14" t="n">
-        <v>1031</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15">
@@ -934,7 +946,7 @@
         <v>91.59999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4980193314692448</v>
+        <v>0.4980193314692444</v>
       </c>
       <c r="J15" t="n">
         <v>583089</v>
@@ -971,7 +983,7 @@
         <v>90.09999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9601614254203767</v>
+        <v>0.9601614254203764</v>
       </c>
       <c r="J16" t="n">
         <v>307213</v>
@@ -983,69 +995,69 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>vitamin_d</t>
+          <t>melatonin</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.73</v>
+        <v>0.43</v>
       </c>
       <c r="E17" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.09</v>
-      </c>
+        <v>1.45</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.001487604635598322</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>426489</v>
+        <v>456</v>
       </c>
       <c r="K17" t="n">
-        <v>19570</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>melatonin</t>
+          <t>vitamin_d</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>0.43</v>
+        <v>0.73</v>
       </c>
       <c r="E18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+        <v>0.91</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.09</v>
+      </c>
       <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
+        <v>70.59999999999999</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.00148760463559832</v>
+      </c>
       <c r="J18" t="n">
-        <v>456</v>
+        <v>426489</v>
       </c>
       <c r="K18" t="n">
-        <v>152</v>
+        <v>19570</v>
       </c>
     </row>
     <row r="19">
@@ -1076,7 +1088,7 @@
         <v>76</v>
       </c>
       <c r="I19" t="n">
-        <v>0.004106812827796202</v>
+        <v>0.004106812827796204</v>
       </c>
       <c r="J19" t="n">
         <v>678322</v>
@@ -1144,7 +1156,7 @@
         <v>77.7</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4473296420997004</v>
+        <v>0.4473296420997003</v>
       </c>
       <c r="J21" t="n">
         <v>739242</v>
@@ -1212,7 +1224,7 @@
         <v>57.3</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4784202102804351</v>
+        <v>0.4784202102804355</v>
       </c>
       <c r="J23" t="n">
         <v>1588466</v>
@@ -1348,7 +1360,7 @@
         <v>86.2</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5204776292170171</v>
+        <v>0.520477629217017</v>
       </c>
       <c r="J27" t="n">
         <v>737543</v>
@@ -1422,7 +1434,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>non-alcoholic_fermented_foods</t>
+          <t>fermented_foods</t>
         </is>
       </c>
       <c r="B30" t="n">
